--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N99_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N99_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>92.06893492530028</v>
+        <v>14.9612019253613</v>
       </c>
       <c r="D2" t="n">
-        <v>87.82511030451371</v>
+        <v>14.27158042448348</v>
       </c>
       <c r="E2" t="n">
-        <v>17.16555467576059</v>
+        <v>2.789402634811095</v>
       </c>
       <c r="F2" t="n">
-        <v>28.67456320428285</v>
+        <v>4.659616520695963</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.94946323481409</v>
+        <v>10.55428777565729</v>
       </c>
       <c r="D3" t="n">
-        <v>57.57820768311566</v>
+        <v>9.356458748506295</v>
       </c>
       <c r="E3" t="n">
-        <v>17.16555467576059</v>
+        <v>2.789402634811095</v>
       </c>
       <c r="F3" t="n">
-        <v>28.67456320428285</v>
+        <v>4.659616520695963</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>75.02413509986826</v>
+        <v>12.19142195372859</v>
       </c>
       <c r="D4" t="n">
-        <v>8.179528492763922</v>
+        <v>1.329173380074137</v>
       </c>
       <c r="E4" t="n">
-        <v>17.16555467576059</v>
+        <v>2.789402634811095</v>
       </c>
       <c r="F4" t="n">
-        <v>28.67456320428285</v>
+        <v>4.659616520695963</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>44.6306432056721</v>
+        <v>7.252479520921717</v>
       </c>
       <c r="D5" t="n">
-        <v>42.54703279900961</v>
+        <v>6.913892829839062</v>
       </c>
       <c r="E5" t="n">
-        <v>17.16555467576059</v>
+        <v>2.789402634811095</v>
       </c>
       <c r="F5" t="n">
-        <v>28.67456320428285</v>
+        <v>4.659616520695963</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
